--- a/E/RPOTA.xlsx
+++ b/E/RPOTA.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="35">
   <si>
     <t/>
   </si>
@@ -43,88 +43,79 @@
     <t>4</t>
   </si>
   <si>
-    <t>20118169</t>
-  </si>
-  <si>
-    <t>KERTAS 1 PLY N101</t>
+    <t>20118173</t>
+  </si>
+  <si>
+    <t>TL.RAPIA GL 1KG N402</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>20131479</t>
+  </si>
+  <si>
+    <t>ROLL STRK EDC MTI</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20131747</t>
+  </si>
+  <si>
+    <t>KARET GELANG</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20136899</t>
+  </si>
+  <si>
+    <t>ROL STRK THERMAL57MM</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20136561</t>
+  </si>
+  <si>
+    <t>APRICOT KARET GELANG</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20054963</t>
+  </si>
+  <si>
+    <t>KNTONG PLST BUAH ROL</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>PT</t>
   </si>
   <si>
-    <t>20118173</t>
-  </si>
-  <si>
-    <t>TL.RAPIA GL 1KG N402</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20131479</t>
-  </si>
-  <si>
-    <t>ROLL STRK EDC MTI</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20131747</t>
-  </si>
-  <si>
-    <t>KARET GELANG</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20136899</t>
-  </si>
-  <si>
-    <t>ROL STRK THERMAL57MM</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20136561</t>
-  </si>
-  <si>
-    <t>APRICOT KARET GELANG</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20054963</t>
-  </si>
-  <si>
-    <t>KNTONG PLST BUAH ROL</t>
+    <t>20118156</t>
+  </si>
+  <si>
+    <t>ROLL STRUK LBL BC4X3</t>
   </si>
   <si>
     <t>18</t>
   </si>
   <si>
-    <t>20118156</t>
-  </si>
-  <si>
-    <t>ROLL STRUK LBL BC4X3</t>
+    <t>20128131</t>
+  </si>
+  <si>
+    <t>ROLL BUAH SEAL 8CM</t>
   </si>
   <si>
     <t>19</t>
-  </si>
-  <si>
-    <t>20128131</t>
-  </si>
-  <si>
-    <t>ROLL BUAH SEAL 8CM</t>
-  </si>
-  <si>
-    <t>20</t>
   </si>
 </sst>
 </file>
@@ -517,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -587,7 +578,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -603,95 +594,95 @@
       <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -712,7 +703,7 @@
         <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -732,26 +723,6 @@
         <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="1" t="s">
         <v>6</v>
       </c>
     </row>
